--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_SR.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_SR.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R76ca8ca1ea0740d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Raff8d20817be4426"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Rd863adc3eed64485"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Rbbbddd9e7d5c4a4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R7a569461ef034eef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R901d65b89bd74d29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R69beaaa526214d81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R65a15cfd240d4b6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R2eb899859f874ff7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R482b0e7bc70e4445"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Raae9313083984853"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Ra35dcb106f984702"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R0cf26e092cf9455e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rd6148881b3154286"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Rce90d1f96bb44249"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R83dde5ea034e405a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R54fe0573a4e14ecc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Raeb2c7eb41b04e89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R17a65370a48e4063"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R40ae75e0ed2d4070"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rdbe2f3462583452d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Re28ce6fba327463f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rf95778f0d54645e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R47cf8f4a29294ab0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R318ff8477fd54a27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R692dd2f6d1304181"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R2565257f77d54220"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R4c79d98d2bcb43fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R863cd53ca7f94e3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R2c0ffd85850b4ec1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R7e5c0c6139534fc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R6300e8cc62c54122"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R269961705fab4215"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Refa0d6a6214545d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R808351bafd8445b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Rf1d5dc3e55ee40e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R080150fb679842ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R8b13c430f7d14f1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R9eadfd4c8b844f4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rcdf82f7c39ac426c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Rec70f45487b44a50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rfe6979bbf8294d05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R3a8c170b800b4052"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2646,6 +2647,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>デルヤ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>タリフ村</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
